--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.57166</v>
+        <v>17.33357</v>
       </c>
       <c r="D2" t="n">
-        <v>17.00891</v>
+        <v>16.95789</v>
       </c>
       <c r="E2" t="n">
-        <v>17.22611</v>
+        <v>17.20238</v>
       </c>
       <c r="F2" t="n">
-        <v>44.47121</v>
+        <v>44.42855</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05168</v>
+        <v>0.053</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86731</v>
+        <v>1.85513</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.59652</v>
+        <v>17.04665</v>
       </c>
       <c r="D3" t="n">
-        <v>17.08348</v>
+        <v>16.75085</v>
       </c>
       <c r="E3" t="n">
-        <v>16.91581</v>
+        <v>17.00413</v>
       </c>
       <c r="F3" t="n">
-        <v>43.39427</v>
+        <v>44.98163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05074</v>
+        <v>0.05127</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86805</v>
+        <v>1.85132</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.27953</v>
+        <v>17.34469</v>
       </c>
       <c r="D4" t="n">
-        <v>17.55149</v>
+        <v>16.71226</v>
       </c>
       <c r="E4" t="n">
-        <v>17.01206</v>
+        <v>17.15314</v>
       </c>
       <c r="F4" t="n">
-        <v>43.56918</v>
+        <v>43.72683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05136</v>
+        <v>0.05252</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8846</v>
+        <v>1.882</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.28602</v>
+        <v>17.30211</v>
       </c>
       <c r="D6" t="n">
-        <v>16.39924</v>
+        <v>16.30799</v>
       </c>
       <c r="E6" t="n">
-        <v>16.94749</v>
+        <v>16.38159</v>
       </c>
       <c r="F6" t="n">
-        <v>22.50438</v>
+        <v>22.72446</v>
       </c>
       <c r="G6" t="n">
-        <v>35.27093</v>
+        <v>35.80743</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.22939</v>
+        <v>16.98769</v>
       </c>
       <c r="D7" t="n">
-        <v>16.47112</v>
+        <v>16.56353</v>
       </c>
       <c r="E7" t="n">
-        <v>16.5934</v>
+        <v>16.80733</v>
       </c>
       <c r="F7" t="n">
-        <v>22.32824</v>
+        <v>22.58486</v>
       </c>
       <c r="G7" t="n">
-        <v>35.07393</v>
+        <v>34.58358</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.23947</v>
+        <v>17.14209</v>
       </c>
       <c r="D8" t="n">
-        <v>16.55401</v>
+        <v>16.76805</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7134</v>
+        <v>16.85374</v>
       </c>
       <c r="F8" t="n">
-        <v>22.4232</v>
+        <v>22.06965</v>
       </c>
       <c r="G8" t="n">
-        <v>35.55879</v>
+        <v>35.54217</v>
       </c>
     </row>
   </sheetData>
